--- a/data/trans_dic/IP38E_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente</t>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,89; 95,12</t>
+          <t>79,2; 95,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,79; 98,06</t>
+          <t>86,76; 97,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,09; 95,73</t>
+          <t>86,51; 95,6</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,03; 95,92</t>
+          <t>82,52; 96,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,57; 93,87</t>
+          <t>78,56; 93,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,46; 93,63</t>
+          <t>83,52; 93,61</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,1; 87,87</t>
+          <t>56,47; 87,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,93; 97,14</t>
+          <t>85,61; 97,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,31; 91,57</t>
+          <t>74,9; 91,78</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,28; 92,36</t>
+          <t>73,9; 91,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,18; 93,06</t>
+          <t>76,23; 92,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,51; 91,27</t>
+          <t>78,7; 91,04</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80,27; 90,39</t>
+          <t>80,42; 90,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,12; 92,46</t>
+          <t>85,06; 92,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,02; 91,0</t>
+          <t>85,05; 90,96</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>34870</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>41964</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>76834</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>31048; 37431</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38548; 43476</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>72351; 79948</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>54978</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>65590</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>120568</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>49749; 58108</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>58576; 69968</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112623; 126228</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>37723</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51861</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>89584</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>27274; 42418</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>47621; 54113</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77839; 95384</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>40675</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54220</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>94895</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>35272; 43698</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>48289; 58759</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>87420; 101129</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>168247</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>213635</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>381882</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>157227; 176039</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>202410; 220819</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368685; 394305</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP38E_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,2; 95,49</t>
+          <t>78,66; 95,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,76; 97,86</t>
+          <t>87,07; 97,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,51; 95,6</t>
+          <t>86,46; 95,86</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,52; 96,38</t>
+          <t>82,19; 95,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,56; 93,84</t>
+          <t>78,55; 94,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,52; 93,61</t>
+          <t>82,85; 93,24</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,47; 87,82</t>
+          <t>60,58; 88,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,61; 97,28</t>
+          <t>85,16; 97,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,9; 91,78</t>
+          <t>76,66; 91,34</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,9; 91,55</t>
+          <t>73,85; 91,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,23; 92,76</t>
+          <t>76,0; 92,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,7; 91,04</t>
+          <t>77,79; 90,56</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80,42; 90,04</t>
+          <t>80,54; 90,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,06; 92,8</t>
+          <t>85,13; 92,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,05; 90,96</t>
+          <t>85,07; 90,66</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31048; 37431</t>
+          <t>30835; 37365</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38548; 43476</t>
+          <t>38684; 43486</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72351; 79948</t>
+          <t>72304; 80171</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49749; 58108</t>
+          <t>49555; 57826</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58576; 69968</t>
+          <t>58564; 70221</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112623; 126228</t>
+          <t>111723; 125738</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27274; 42418</t>
+          <t>29258; 42686</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47621; 54113</t>
+          <t>47374; 53977</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77839; 95384</t>
+          <t>79674; 94928</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35272; 43698</t>
+          <t>35247; 43832</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48289; 58759</t>
+          <t>48143; 58481</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87420; 101129</t>
+          <t>86409; 100593</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>157227; 176039</t>
+          <t>157476; 176004</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202410; 220819</t>
+          <t>202587; 220907</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>368685; 394305</t>
+          <t>368776; 392975</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38E_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,66; 95,32</t>
+          <t>88,24; 98,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,07; 97,88</t>
+          <t>77,43; 94,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,46; 95,86</t>
+          <t>85,39; 95,57</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,19; 95,91</t>
+          <t>78,15; 93,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,55; 94,18</t>
+          <t>81,94; 95,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,85; 93,24</t>
+          <t>82,81; 93,35</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,58; 88,38</t>
+          <t>84,04; 97,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,16; 97,03</t>
+          <t>70,56; 90,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,66; 91,34</t>
+          <t>80,13; 92,22</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,85; 91,83</t>
+          <t>74,49; 92,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,0; 92,32</t>
+          <t>74,66; 92,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,79; 90,56</t>
+          <t>78,53; 91,25</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80,54; 90,02</t>
+          <t>84,72; 92,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,13; 92,83</t>
+          <t>82,0; 90,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,07; 90,66</t>
+          <t>85,25; 91,16</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>59</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34870</t>
+          <t>38680</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>36251</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76834</t>
+          <t>74931</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30835; 37365</t>
+          <t>35993; 40131</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38684; 43486</t>
+          <t>31698; 38883</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72304; 80171</t>
+          <t>69787; 78109</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>54978</t>
+          <t>60354</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65590</t>
+          <t>53117</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120568</t>
+          <t>113472</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49555; 57826</t>
+          <t>53865; 64572</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58564; 70221</t>
+          <t>48066; 56175</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111723; 125738</t>
+          <t>105659; 119101</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37723</t>
+          <t>46689</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51861</t>
+          <t>35657</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89584</t>
+          <t>82345</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29258; 42686</t>
+          <t>42118; 48685</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47374; 53977</t>
+          <t>30931; 39469</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79674; 94928</t>
+          <t>75282; 86640</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>60</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>40675</t>
+          <t>51963</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>54220</t>
+          <t>41973</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94895</t>
+          <t>93936</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35247; 43832</t>
+          <t>45408; 56585</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48143; 58481</t>
+          <t>36666; 45494</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86409; 100593</t>
+          <t>86435; 100434</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>247</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>168247</t>
+          <t>197686</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>213635</t>
+          <t>166998</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>381882</t>
+          <t>364684</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>157476; 176004</t>
+          <t>187060; 203898</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202587; 220907</t>
+          <t>157881; 174815</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>368776; 392975</t>
+          <t>352379; 376801</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38E_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>94,83%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>88,55%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>91,68%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>88,24; 98,39</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>77,43; 94,98</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>85,39; 95,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>87,56%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>90,55%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>78,15; 93,68</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>81,94; 95,77</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>82,81; 93,35</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>93,17%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>81,35%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>87,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>84,04; 97,15</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>70,56; 90,04</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>80,13; 92,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>85,25%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>85,47%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>85,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>74,49; 92,83</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>74,66; 92,63</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78,53; 91,25</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>89,54%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>86,73%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>88,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>84,72; 92,35</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>82,0; 90,79</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>85,25; 91,16</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9483103737225779</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.885479276345988</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9168368160568366</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>38680</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>36251</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>74931</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.88244849077709</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.7742648472019699</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8538877919272797</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>35993; 40131</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>31698; 38883</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>69787; 78109</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9838981081945252</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9497752756380032</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9557128529032095</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.8756001745996043</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9055356523185685</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.889362961641973</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>60354</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>53117</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>113472</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.7814594304272595</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8194193980807936</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8281264731131609</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>53865; 64572</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>48066; 56175</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>105659; 119101</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9367828802422856</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9576719818021694</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9334777206962976</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9316564631677327</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8134699793014706</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8765140146679857</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>46689</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>35657</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>82345</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.840449315723371</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.7056497740163685</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8013365461138886</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>42118; 48685</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>30931; 39469</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>75282; 86640</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.971488059870881</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9004458250370949</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9222275313645354</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8524816326224665</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8546515171432858</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8534498316929895</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>51963</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>41973</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>93936</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.7449375115372489</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.7465907152932008</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.7853054529391603</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>45408; 56585</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>36666; 45494</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>86435; 100434</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9283101345371972</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9263467432756038</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9124869061465879</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.8953737853545477</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8673331533679137</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8823115464351646</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>197686</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>166998</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>364684</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8472461812517955</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.8199807980237833</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.852541473976632</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>187060; 203898</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>157881; 174815</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>352379; 376801</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9235097441168798</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.90793306823441</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9116282177273293</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>38680</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>36251</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>74931</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>35993</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>31698</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>69787</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>40131</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>38883</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>78109</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>60354</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>53117</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>113472</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>53865</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>48066</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>105659</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>64572</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>56175</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>119101</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>46689</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>35657</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>82345</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>42118</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>30931</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>75282</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>48685</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>39469</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>86640</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>51963</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>41973</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>93936</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>45408</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>36666</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>86435</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>56585</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>45494</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>100434</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>285</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>247</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>197686</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>166998</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>364684</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>187060</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>157881</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>352379</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>203898</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>174815</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>376801</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>